--- a/NURBS IDX30 PYTHON ANALYSIS/Back_final_15_2_26/15gps/2mps_analysis.xlsx
+++ b/NURBS IDX30 PYTHON ANALYSIS/Back_final_15_2_26/15gps/2mps_analysis.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>Time</t>
   </si>
@@ -79,13 +79,34 @@
     <t>Q</t>
   </si>
   <si>
-    <t>rolling_std</t>
-  </si>
-  <si>
     <t>steady_state</t>
   </si>
   <si>
-    <t>avg_Q_steady</t>
+    <t>Averages</t>
+  </si>
+  <si>
+    <t>RTD_OUT_unc</t>
+  </si>
+  <si>
+    <t>RTD_IN_unc</t>
+  </si>
+  <si>
+    <t>RTD_unc</t>
+  </si>
+  <si>
+    <t>Delta_RTD</t>
+  </si>
+  <si>
+    <t>Rel_unc</t>
+  </si>
+  <si>
+    <t>ABS_unc</t>
+  </si>
+  <si>
+    <t>Average Q (W)</t>
+  </si>
+  <si>
+    <t>Average Q Uncertainty (W)</t>
   </si>
 </sst>
 </file>
@@ -421,10 +442,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:X57"/>
+  <dimension ref="A1:AC57"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:29">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -497,8 +518,23 @@
       <c r="X1" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="2" spans="1:24">
+      <c r="Y1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:29">
       <c r="A2" s="1">
         <v>46068.54216884259</v>
       </c>
@@ -562,14 +598,32 @@
       <c r="U2">
         <v>385.825979417178</v>
       </c>
-      <c r="W2" t="b">
+      <c r="V2" t="b">
         <v>0</v>
       </c>
+      <c r="W2" t="s">
+        <v>29</v>
+      </c>
       <c r="X2">
-        <v>389.1123109761087</v>
-      </c>
-    </row>
-    <row r="3" spans="1:24">
+        <v>0.249551622</v>
+      </c>
+      <c r="Y2">
+        <v>0.26123615</v>
+      </c>
+      <c r="Z2">
+        <v>0.3612759860683427</v>
+      </c>
+      <c r="AA2">
+        <v>5.842264</v>
+      </c>
+      <c r="AB2">
+        <v>0.06264169502048102</v>
+      </c>
+      <c r="AC2">
+        <v>24.16879333362925</v>
+      </c>
+    </row>
+    <row r="3" spans="1:29">
       <c r="A3" s="1">
         <v>46068.54228458333</v>
       </c>
@@ -633,11 +687,32 @@
       <c r="U3">
         <v>384.5170680427864</v>
       </c>
-      <c r="W3" t="b">
+      <c r="V3" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:24">
+      <c r="W3">
+        <v>389.17826830836</v>
+      </c>
+      <c r="X3">
+        <v>0.249557022</v>
+      </c>
+      <c r="Y3">
+        <v>0.261227558</v>
+      </c>
+      <c r="Z3">
+        <v>0.3612735034404708</v>
+      </c>
+      <c r="AA3">
+        <v>5.835267999999999</v>
+      </c>
+      <c r="AB3">
+        <v>0.06271446437240639</v>
+      </c>
+      <c r="AC3">
+        <v>24.1147819643515</v>
+      </c>
+    </row>
+    <row r="4" spans="1:29">
       <c r="A4" s="1">
         <v>46068.54240032408</v>
       </c>
@@ -701,14 +776,32 @@
       <c r="U4">
         <v>386.8111926802297</v>
       </c>
-      <c r="V4">
-        <v>1.15086214145664</v>
-      </c>
-      <c r="W4" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:24">
+      <c r="V4" t="b">
+        <v>0</v>
+      </c>
+      <c r="W4" t="s">
+        <v>30</v>
+      </c>
+      <c r="X4">
+        <v>0.24954209</v>
+      </c>
+      <c r="Y4">
+        <v>0.261237424</v>
+      </c>
+      <c r="Z4">
+        <v>0.3612703231372927</v>
+      </c>
+      <c r="AA4">
+        <v>5.847667000000001</v>
+      </c>
+      <c r="AB4">
+        <v>0.06258433639857096</v>
+      </c>
+      <c r="AC4">
+        <v>24.20832180543195</v>
+      </c>
+    </row>
+    <row r="5" spans="1:29">
       <c r="A5" s="1">
         <v>46068.54251664352</v>
       </c>
@@ -772,14 +865,32 @@
       <c r="U5">
         <v>384.6976932414453</v>
       </c>
-      <c r="V5">
-        <v>1.275572629074046</v>
-      </c>
-      <c r="W5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:24">
+      <c r="V5" t="b">
+        <v>0</v>
+      </c>
+      <c r="W5">
+        <v>24.12852993862252</v>
+      </c>
+      <c r="X5">
+        <v>0.249526838</v>
+      </c>
+      <c r="Y5">
+        <v>0.261219918</v>
+      </c>
+      <c r="Z5">
+        <v>0.3612471293203656</v>
+      </c>
+      <c r="AA5">
+        <v>5.846540000000005</v>
+      </c>
+      <c r="AB5">
+        <v>0.0625921762544389</v>
+      </c>
+      <c r="AC5">
+        <v>24.07906582004461</v>
+      </c>
+    </row>
+    <row r="6" spans="1:29">
       <c r="A6" s="1">
         <v>46068.54263296296</v>
       </c>
@@ -843,14 +954,29 @@
       <c r="U6">
         <v>385.8188350918356</v>
       </c>
-      <c r="V6">
-        <v>1.05740346365379</v>
-      </c>
-      <c r="W6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:24">
+      <c r="V6" t="b">
+        <v>0</v>
+      </c>
+      <c r="X6">
+        <v>0.249522708</v>
+      </c>
+      <c r="Y6">
+        <v>0.261224056</v>
+      </c>
+      <c r="Z6">
+        <v>0.3612472688349967</v>
+      </c>
+      <c r="AA6">
+        <v>5.850674000000005</v>
+      </c>
+      <c r="AB6">
+        <v>0.06254910234503464</v>
+      </c>
+      <c r="AC6">
+        <v>24.13262180280127</v>
+      </c>
+    </row>
+    <row r="7" spans="1:29">
       <c r="A7" s="1">
         <v>46068.54274928241</v>
       </c>
@@ -914,14 +1040,29 @@
       <c r="U7">
         <v>385.5267509804794</v>
       </c>
-      <c r="V7">
-        <v>0.5816082460809009</v>
-      </c>
-      <c r="W7" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:24">
+      <c r="V7" t="b">
+        <v>0</v>
+      </c>
+      <c r="X7">
+        <v>0.249506822</v>
+      </c>
+      <c r="Y7">
+        <v>0.261217692</v>
+      </c>
+      <c r="Z7">
+        <v>0.3612316941221334</v>
+      </c>
+      <c r="AA7">
+        <v>5.855435</v>
+      </c>
+      <c r="AB7">
+        <v>0.06249691908433642</v>
+      </c>
+      <c r="AC7">
+        <v>24.09423416087414</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29">
       <c r="A8" s="1">
         <v>46068.54286560185</v>
       </c>
@@ -985,14 +1126,29 @@
       <c r="U8">
         <v>386.9110427717466</v>
       </c>
-      <c r="V8">
-        <v>0.7296682473943159</v>
-      </c>
-      <c r="W8" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:24">
+      <c r="V8" t="b">
+        <v>0</v>
+      </c>
+      <c r="X8">
+        <v>0.2494849</v>
+      </c>
+      <c r="Y8">
+        <v>0.26120687</v>
+      </c>
+      <c r="Z8">
+        <v>0.3612087267262613</v>
+      </c>
+      <c r="AA8">
+        <v>5.860984999999999</v>
+      </c>
+      <c r="AB8">
+        <v>0.0624353860363276</v>
+      </c>
+      <c r="AC8">
+        <v>24.15694031717206</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29">
       <c r="A9" s="1">
         <v>46068.54298192129</v>
       </c>
@@ -1056,14 +1212,29 @@
       <c r="U9">
         <v>386.6348082884229</v>
       </c>
-      <c r="V9">
-        <v>0.7326163446663683</v>
-      </c>
-      <c r="W9" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:24">
+      <c r="V9" t="b">
+        <v>0</v>
+      </c>
+      <c r="X9">
+        <v>0.249481088</v>
+      </c>
+      <c r="Y9">
+        <v>0.261211962</v>
+      </c>
+      <c r="Z9">
+        <v>0.3612097761156987</v>
+      </c>
+      <c r="AA9">
+        <v>5.865437</v>
+      </c>
+      <c r="AB9">
+        <v>0.06238938889981726</v>
+      </c>
+      <c r="AC9">
+        <v>24.12190941651271</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29">
       <c r="A10" s="1">
         <v>46068.54309824074</v>
       </c>
@@ -1127,14 +1298,29 @@
       <c r="U10">
         <v>386.615325912046</v>
       </c>
-      <c r="V10">
-        <v>0.1653952407002974</v>
-      </c>
-      <c r="W10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:24">
+      <c r="V10" t="b">
+        <v>0</v>
+      </c>
+      <c r="X10">
+        <v>0.24946552</v>
+      </c>
+      <c r="Y10">
+        <v>0.261198276</v>
+      </c>
+      <c r="Z10">
+        <v>0.3611891264341198</v>
+      </c>
+      <c r="AA10">
+        <v>5.866378000000005</v>
+      </c>
+      <c r="AB10">
+        <v>0.06237616393707219</v>
+      </c>
+      <c r="AC10">
+        <v>24.11558094967437</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29">
       <c r="A11" s="1">
         <v>46068.54321456019</v>
       </c>
@@ -1198,14 +1384,29 @@
       <c r="U11">
         <v>385.7264759409733</v>
       </c>
-      <c r="V11">
-        <v>0.5188932914528653</v>
-      </c>
-      <c r="W11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:24">
+      <c r="V11" t="b">
+        <v>0</v>
+      </c>
+      <c r="X11">
+        <v>0.249465838</v>
+      </c>
+      <c r="Y11">
+        <v>0.261198276</v>
+      </c>
+      <c r="Z11">
+        <v>0.3611893460699172</v>
+      </c>
+      <c r="AA11">
+        <v>5.866219000000001</v>
+      </c>
+      <c r="AB11">
+        <v>0.06237784810594386</v>
+      </c>
+      <c r="AC11">
+        <v>24.06078752668704</v>
+      </c>
+    </row>
+    <row r="12" spans="1:29">
       <c r="A12" s="1">
         <v>46068.54333087963</v>
       </c>
@@ -1269,14 +1470,29 @@
       <c r="U12">
         <v>387.3742227546891</v>
       </c>
-      <c r="V12">
-        <v>0.8247270509043386</v>
-      </c>
-      <c r="W12" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:24">
+      <c r="V12" t="b">
+        <v>0</v>
+      </c>
+      <c r="X12">
+        <v>0.249457894</v>
+      </c>
+      <c r="Y12">
+        <v>0.261189364</v>
+      </c>
+      <c r="Z12">
+        <v>0.3611774145010174</v>
+      </c>
+      <c r="AA12">
+        <v>5.865735000000001</v>
+      </c>
+      <c r="AB12">
+        <v>0.06238085501387858</v>
+      </c>
+      <c r="AC12">
+        <v>24.16473522577417</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29">
       <c r="A13" s="1">
         <v>46068.54344719907</v>
       </c>
@@ -1340,14 +1556,29 @@
       <c r="U13">
         <v>385.9194846756463</v>
       </c>
-      <c r="V13">
-        <v>0.9007945393177398</v>
-      </c>
-      <c r="W13" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:24">
+      <c r="V13" t="b">
+        <v>0</v>
+      </c>
+      <c r="X13">
+        <v>0.24945853</v>
+      </c>
+      <c r="Y13">
+        <v>0.26119573</v>
+      </c>
+      <c r="Z13">
+        <v>0.3611824574366726</v>
+      </c>
+      <c r="AA13">
+        <v>5.868600000000001</v>
+      </c>
+      <c r="AB13">
+        <v>0.06235203218635234</v>
+      </c>
+      <c r="AC13">
+        <v>24.06286412983641</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29">
       <c r="A14" s="1">
         <v>46068.54356293981</v>
       </c>
@@ -1411,14 +1642,29 @@
       <c r="U14">
         <v>386.5693843040817</v>
       </c>
-      <c r="V14">
-        <v>0.7287429058812992</v>
-      </c>
-      <c r="W14" t="b">
+      <c r="V14" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="15" spans="1:24">
+      <c r="X14">
+        <v>0.249444868</v>
+      </c>
+      <c r="Y14">
+        <v>0.261194138</v>
+      </c>
+      <c r="Z14">
+        <v>0.3611718703015234</v>
+      </c>
+      <c r="AA14">
+        <v>5.874634999999998</v>
+      </c>
+      <c r="AB14">
+        <v>0.06228784767797137</v>
+      </c>
+      <c r="AC14">
+        <v>24.07857492649982</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29">
       <c r="A15" s="1">
         <v>46068.54367868056</v>
       </c>
@@ -1482,14 +1728,29 @@
       <c r="U15">
         <v>387.7907334643264</v>
       </c>
-      <c r="V15">
-        <v>0.9500557288397729</v>
-      </c>
-      <c r="W15" t="b">
+      <c r="V15" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="16" spans="1:24">
+      <c r="X15">
+        <v>0.24943756</v>
+      </c>
+      <c r="Y15">
+        <v>0.261196048</v>
+      </c>
+      <c r="Z15">
+        <v>0.3611682043446958</v>
+      </c>
+      <c r="AA15">
+        <v>5.879244</v>
+      </c>
+      <c r="AB15">
+        <v>0.06223966109560702</v>
+      </c>
+      <c r="AC15">
+        <v>24.13596382683654</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29">
       <c r="A16" s="1">
         <v>46068.5437944213</v>
       </c>
@@ -1553,14 +1814,29 @@
       <c r="U16">
         <v>387.8680908297645</v>
       </c>
-      <c r="V16">
-        <v>0.7285049271245905</v>
-      </c>
-      <c r="W16" t="b">
+      <c r="V16" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="17" spans="1:23">
+      <c r="X16">
+        <v>0.249436608</v>
+      </c>
+      <c r="Y16">
+        <v>0.26119191</v>
+      </c>
+      <c r="Z16">
+        <v>0.3611645542685408</v>
+      </c>
+      <c r="AA16">
+        <v>5.877650999999993</v>
+      </c>
+      <c r="AB16">
+        <v>0.06225548135721982</v>
+      </c>
+      <c r="AC16">
+        <v>24.14691469771285</v>
+      </c>
+    </row>
+    <row r="17" spans="1:29">
       <c r="A17" s="1">
         <v>46068.54391074074</v>
       </c>
@@ -1624,14 +1900,29 @@
       <c r="U17">
         <v>388.3032866679989</v>
       </c>
-      <c r="V17">
-        <v>0.2763121321375649</v>
-      </c>
-      <c r="W17" t="b">
+      <c r="V17" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="18" spans="1:23">
+      <c r="X17">
+        <v>0.249420086</v>
+      </c>
+      <c r="Y17">
+        <v>0.261201778</v>
+      </c>
+      <c r="Z17">
+        <v>0.3611602803889274</v>
+      </c>
+      <c r="AA17">
+        <v>5.890846000000003</v>
+      </c>
+      <c r="AB17">
+        <v>0.06211892013698905</v>
+      </c>
+      <c r="AC17">
+        <v>24.12098085345979</v>
+      </c>
+    </row>
+    <row r="18" spans="1:29">
       <c r="A18" s="1">
         <v>46068.54402706018</v>
       </c>
@@ -1695,14 +1986,29 @@
       <c r="U18">
         <v>389.1348904826395</v>
       </c>
-      <c r="V18">
-        <v>0.6436538514171023</v>
-      </c>
-      <c r="W18" t="b">
+      <c r="V18" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="19" spans="1:23">
+      <c r="X18">
+        <v>0.249419768</v>
+      </c>
+      <c r="Y18">
+        <v>0.26120687</v>
+      </c>
+      <c r="Z18">
+        <v>0.3611637434798387</v>
+      </c>
+      <c r="AA18">
+        <v>5.893550999999995</v>
+      </c>
+      <c r="AB18">
+        <v>0.06209172799574733</v>
+      </c>
+      <c r="AC18">
+        <v>24.16205777350298</v>
+      </c>
+    </row>
+    <row r="19" spans="1:29">
       <c r="A19" s="1">
         <v>46068.54414280093</v>
       </c>
@@ -1766,14 +2072,29 @@
       <c r="U19">
         <v>389.2560260705588</v>
       </c>
-      <c r="V19">
-        <v>0.5186442429344652</v>
-      </c>
-      <c r="W19" t="b">
+      <c r="V19" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="20" spans="1:23">
+      <c r="X19">
+        <v>0.249414684</v>
+      </c>
+      <c r="Y19">
+        <v>0.261211962</v>
+      </c>
+      <c r="Z19">
+        <v>0.3611639152610754</v>
+      </c>
+      <c r="AA19">
+        <v>5.898639000000003</v>
+      </c>
+      <c r="AB19">
+        <v>0.06203958793369466</v>
+      </c>
+      <c r="AC19">
+        <v>24.14928345812498</v>
+      </c>
+    </row>
+    <row r="20" spans="1:29">
       <c r="A20" s="1">
         <v>46068.54425912037</v>
       </c>
@@ -1837,14 +2158,29 @@
       <c r="U20">
         <v>389.3384679474301</v>
       </c>
-      <c r="V20">
-        <v>0.1023997704194226</v>
-      </c>
-      <c r="W20" t="b">
+      <c r="V20" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="21" spans="1:23">
+      <c r="X20">
+        <v>0.24943216</v>
+      </c>
+      <c r="Y20">
+        <v>0.261223102</v>
+      </c>
+      <c r="Z20">
+        <v>0.3611840409829427</v>
+      </c>
+      <c r="AA20">
+        <v>5.895471000000001</v>
+      </c>
+      <c r="AB20">
+        <v>0.06207542886634246</v>
+      </c>
+      <c r="AC20">
+        <v>24.16835237200145</v>
+      </c>
+    </row>
+    <row r="21" spans="1:29">
       <c r="A21" s="1">
         <v>46068.54437543981</v>
       </c>
@@ -1908,14 +2244,29 @@
       <c r="U21">
         <v>389.3875821880044</v>
       </c>
-      <c r="V21">
-        <v>0.06647792080218616</v>
-      </c>
-      <c r="W21" t="b">
+      <c r="V21" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="22" spans="1:23">
+      <c r="X21">
+        <v>0.249424216</v>
+      </c>
+      <c r="Y21">
+        <v>0.261220874</v>
+      </c>
+      <c r="Z21">
+        <v>0.3611769435339672</v>
+      </c>
+      <c r="AA21">
+        <v>5.898328999999997</v>
+      </c>
+      <c r="AB21">
+        <v>0.06204494377947754</v>
+      </c>
+      <c r="AC21">
+        <v>24.15953064528142</v>
+      </c>
+    </row>
+    <row r="22" spans="1:29">
       <c r="A22" s="1">
         <v>46068.54449118055</v>
       </c>
@@ -1979,14 +2330,29 @@
       <c r="U22">
         <v>389.8103402915213</v>
       </c>
-      <c r="V22">
-        <v>0.259422477769689</v>
-      </c>
-      <c r="W22" t="b">
+      <c r="V22" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="23" spans="1:23">
+      <c r="X22">
+        <v>0.249413732</v>
+      </c>
+      <c r="Y22">
+        <v>0.261229468</v>
+      </c>
+      <c r="Z22">
+        <v>0.3611759192716631</v>
+      </c>
+      <c r="AA22">
+        <v>5.907868000000001</v>
+      </c>
+      <c r="AB22">
+        <v>0.06194719767211325</v>
+      </c>
+      <c r="AC22">
+        <v>24.1476582046726</v>
+      </c>
+    </row>
+    <row r="23" spans="1:29">
       <c r="A23" s="1">
         <v>46068.5446075</v>
       </c>
@@ -2050,14 +2416,29 @@
       <c r="U23">
         <v>389.081353853375</v>
       </c>
-      <c r="V23">
-        <v>0.3660422184254123</v>
-      </c>
-      <c r="W23" t="b">
+      <c r="V23" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="24" spans="1:23">
+      <c r="X23">
+        <v>0.24941818</v>
+      </c>
+      <c r="Y23">
+        <v>0.261231376</v>
+      </c>
+      <c r="Z23">
+        <v>0.3611803708970987</v>
+      </c>
+      <c r="AA23">
+        <v>5.906597999999995</v>
+      </c>
+      <c r="AB23">
+        <v>0.06196091390743674</v>
+      </c>
+      <c r="AC23">
+        <v>24.10783626909789</v>
+      </c>
+    </row>
+    <row r="24" spans="1:29">
       <c r="A24" s="1">
         <v>46068.54472381945</v>
       </c>
@@ -2121,14 +2502,29 @@
       <c r="U24">
         <v>390.217308410885</v>
       </c>
-      <c r="V24">
-        <v>0.5755341046810257</v>
-      </c>
-      <c r="W24" t="b">
+      <c r="V24" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="25" spans="1:23">
+      <c r="X24">
+        <v>0.249418816</v>
+      </c>
+      <c r="Y24">
+        <v>0.261252702</v>
+      </c>
+      <c r="Z24">
+        <v>0.3611962348601417</v>
+      </c>
+      <c r="AA24">
+        <v>5.916942999999996</v>
+      </c>
+      <c r="AB24">
+        <v>0.0618580533392346</v>
+      </c>
+      <c r="AC24">
+        <v>24.13808307757309</v>
+      </c>
+    </row>
+    <row r="25" spans="1:29">
       <c r="A25" s="1">
         <v>46068.54483956019</v>
       </c>
@@ -2192,14 +2588,29 @@
       <c r="U25">
         <v>390.1769010668555</v>
       </c>
-      <c r="V25">
-        <v>0.6444958245459095</v>
-      </c>
-      <c r="W25" t="b">
+      <c r="V25" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="26" spans="1:23">
+      <c r="X25">
+        <v>0.249412778</v>
+      </c>
+      <c r="Y25">
+        <v>0.261245062</v>
+      </c>
+      <c r="Z25">
+        <v>0.3611865394073554</v>
+      </c>
+      <c r="AA25">
+        <v>5.916142000000001</v>
+      </c>
+      <c r="AB25">
+        <v>0.06186459231892466</v>
+      </c>
+      <c r="AC25">
+        <v>24.13813491676242</v>
+      </c>
+    </row>
+    <row r="26" spans="1:29">
       <c r="A26" s="1">
         <v>46068.54495587963</v>
       </c>
@@ -2263,14 +2674,29 @@
       <c r="U26">
         <v>389.1650744239252</v>
       </c>
-      <c r="V26">
-        <v>0.5961854118905782</v>
-      </c>
-      <c r="W26" t="b">
+      <c r="V26" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="27" spans="1:23">
+      <c r="X26">
+        <v>0.24942104</v>
+      </c>
+      <c r="Y26">
+        <v>0.261251746</v>
+      </c>
+      <c r="Z26">
+        <v>0.3611970791447933</v>
+      </c>
+      <c r="AA26">
+        <v>5.915352999999996</v>
+      </c>
+      <c r="AB26">
+        <v>0.06187438667138932</v>
+      </c>
+      <c r="AC26">
+        <v>24.07935029390595</v>
+      </c>
+    </row>
+    <row r="27" spans="1:29">
       <c r="A27" s="1">
         <v>46068.54507219907</v>
       </c>
@@ -2334,14 +2760,29 @@
       <c r="U27">
         <v>390.5304185085901</v>
       </c>
-      <c r="V27">
-        <v>0.7086292173957859</v>
-      </c>
-      <c r="W27" t="b">
+      <c r="V27" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="28" spans="1:23">
+      <c r="X27">
+        <v>0.24943756</v>
+      </c>
+      <c r="Y27">
+        <v>0.261266388</v>
+      </c>
+      <c r="Z27">
+        <v>0.3612190773440962</v>
+      </c>
+      <c r="AA27">
+        <v>5.914414000000001</v>
+      </c>
+      <c r="AB27">
+        <v>0.06188762410816</v>
+      </c>
+      <c r="AC27">
+        <v>24.16899974346203</v>
+      </c>
+    </row>
+    <row r="28" spans="1:29">
       <c r="A28" s="1">
         <v>46068.54518851852</v>
       </c>
@@ -2405,14 +2846,29 @@
       <c r="U28">
         <v>392.0463659967335</v>
       </c>
-      <c r="V28">
-        <v>1.441301633008198</v>
-      </c>
-      <c r="W28" t="b">
+      <c r="V28" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="29" spans="1:23">
+      <c r="X28">
+        <v>0.249437242</v>
+      </c>
+      <c r="Y28">
+        <v>0.26126957</v>
+      </c>
+      <c r="Z28">
+        <v>0.3612211592702613</v>
+      </c>
+      <c r="AA28">
+        <v>5.916164000000002</v>
+      </c>
+      <c r="AB28">
+        <v>0.0618701430719984</v>
+      </c>
+      <c r="AC28">
+        <v>24.25596475507495</v>
+      </c>
+    </row>
+    <row r="29" spans="1:29">
       <c r="A29" s="1">
         <v>46068.54530425926</v>
       </c>
@@ -2476,14 +2932,29 @@
       <c r="U29">
         <v>390.0228737301093</v>
       </c>
-      <c r="V29">
-        <v>1.05279148315786</v>
-      </c>
-      <c r="W29" t="b">
+      <c r="V29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="30" spans="1:23">
+      <c r="X29">
+        <v>0.249435972</v>
+      </c>
+      <c r="Y29">
+        <v>0.261272752</v>
+      </c>
+      <c r="Z29">
+        <v>0.3612225838250404</v>
+      </c>
+      <c r="AA29">
+        <v>5.918389999999995</v>
+      </c>
+      <c r="AB29">
+        <v>0.06184771828912806</v>
+      </c>
+      <c r="AC29">
+        <v>24.12202482077596</v>
+      </c>
+    </row>
+    <row r="30" spans="1:29">
       <c r="A30" s="1">
         <v>46068.5454205787</v>
       </c>
@@ -2547,14 +3018,29 @@
       <c r="U30">
         <v>389.896756625775</v>
       </c>
-      <c r="V30">
-        <v>1.20631994959913</v>
-      </c>
-      <c r="W30" t="b">
+      <c r="V30" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="31" spans="1:23">
+      <c r="X30">
+        <v>0.249443596</v>
+      </c>
+      <c r="Y30">
+        <v>0.261271798</v>
+      </c>
+      <c r="Z30">
+        <v>0.3612271584689667</v>
+      </c>
+      <c r="AA30">
+        <v>5.914101000000002</v>
+      </c>
+      <c r="AB30">
+        <v>0.06189216241903699</v>
+      </c>
+      <c r="AC30">
+        <v>24.1315533877382</v>
+      </c>
+    </row>
+    <row r="31" spans="1:29">
       <c r="A31" s="1">
         <v>46068.54553689815</v>
       </c>
@@ -2618,14 +3104,29 @@
       <c r="U31">
         <v>389.8151770716958</v>
       </c>
-      <c r="V31">
-        <v>0.1046411722374879</v>
-      </c>
-      <c r="W31" t="b">
+      <c r="V31" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="32" spans="1:23">
+      <c r="X31">
+        <v>0.249451858</v>
+      </c>
+      <c r="Y31">
+        <v>0.261277846</v>
+      </c>
+      <c r="Z31">
+        <v>0.3612372382106417</v>
+      </c>
+      <c r="AA31">
+        <v>5.912993999999998</v>
+      </c>
+      <c r="AB31">
+        <v>0.06190512937765984</v>
+      </c>
+      <c r="AC31">
+        <v>24.13155896999871</v>
+      </c>
+    </row>
+    <row r="32" spans="1:29">
       <c r="A32" s="1">
         <v>46068.5456532176</v>
       </c>
@@ -2689,14 +3190,29 @@
       <c r="U32">
         <v>389.4730584941744</v>
       </c>
-      <c r="V32">
-        <v>0.2248037853509114</v>
-      </c>
-      <c r="W32" t="b">
+      <c r="V32" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="33" spans="1:23">
+      <c r="X32">
+        <v>0.249448998</v>
+      </c>
+      <c r="Y32">
+        <v>0.261283574</v>
+      </c>
+      <c r="Z32">
+        <v>0.3612394062743121</v>
+      </c>
+      <c r="AA32">
+        <v>5.917287999999999</v>
+      </c>
+      <c r="AB32">
+        <v>0.06186174088563933</v>
+      </c>
+      <c r="AC32">
+        <v>24.09348142650407</v>
+      </c>
+    </row>
+    <row r="33" spans="1:29">
       <c r="A33" s="1">
         <v>46068.54576953704</v>
       </c>
@@ -2760,14 +3276,29 @@
       <c r="U33">
         <v>389.0960079723443</v>
       </c>
-      <c r="V33">
-        <v>0.359725916626643</v>
-      </c>
-      <c r="W33" t="b">
+      <c r="V33" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="34" spans="1:23">
+      <c r="X33">
+        <v>0.249455352</v>
+      </c>
+      <c r="Y33">
+        <v>0.261296942</v>
+      </c>
+      <c r="Z33">
+        <v>0.3612534630145368</v>
+      </c>
+      <c r="AA33">
+        <v>5.920794999999998</v>
+      </c>
+      <c r="AB33">
+        <v>0.06182839963042016</v>
+      </c>
+      <c r="AC33">
+        <v>24.05718347551525</v>
+      </c>
+    </row>
+    <row r="34" spans="1:29">
       <c r="A34" s="1">
         <v>46068.54588585648</v>
       </c>
@@ -2831,14 +3362,29 @@
       <c r="U34">
         <v>390.1350196371683</v>
       </c>
-      <c r="V34">
-        <v>0.5259760594177988</v>
-      </c>
-      <c r="W34" t="b">
+      <c r="V34" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="35" spans="1:23">
+      <c r="X34">
+        <v>0.249476322</v>
+      </c>
+      <c r="Y34">
+        <v>0.261294396</v>
+      </c>
+      <c r="Z34">
+        <v>0.3612661022288868</v>
+      </c>
+      <c r="AA34">
+        <v>5.909037000000005</v>
+      </c>
+      <c r="AB34">
+        <v>0.06195032356119681</v>
+      </c>
+      <c r="AC34">
+        <v>24.16899069907645</v>
+      </c>
+    </row>
+    <row r="35" spans="1:29">
       <c r="A35" s="1">
         <v>46068.54600159722</v>
       </c>
@@ -2902,14 +3448,29 @@
       <c r="U35">
         <v>389.5983358679488</v>
       </c>
-      <c r="V35">
-        <v>0.5196004911602802</v>
-      </c>
-      <c r="W35" t="b">
+      <c r="V35" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="36" spans="1:23">
+      <c r="X35">
+        <v>0.249481088</v>
+      </c>
+      <c r="Y35">
+        <v>0.261307446</v>
+      </c>
+      <c r="Z35">
+        <v>0.3612788322123324</v>
+      </c>
+      <c r="AA35">
+        <v>5.913179</v>
+      </c>
+      <c r="AB35">
+        <v>0.06191018489147113</v>
+      </c>
+      <c r="AC35">
+        <v>24.12010500699418</v>
+      </c>
+    </row>
+    <row r="36" spans="1:29">
       <c r="A36" s="1">
         <v>46068.54611733797</v>
       </c>
@@ -2973,14 +3534,29 @@
       <c r="U36">
         <v>389.3794706514108</v>
       </c>
-      <c r="V36">
-        <v>0.3887556475539969</v>
-      </c>
-      <c r="W36" t="b">
+      <c r="V36" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="37" spans="1:23">
+      <c r="X36">
+        <v>0.24949189</v>
+      </c>
+      <c r="Y36">
+        <v>0.261310946</v>
+      </c>
+      <c r="Z36">
+        <v>0.3612888230698357</v>
+      </c>
+      <c r="AA36">
+        <v>5.909528000000002</v>
+      </c>
+      <c r="AB36">
+        <v>0.06194910482429093</v>
+      </c>
+      <c r="AC36">
+        <v>24.12170964381116</v>
+      </c>
+    </row>
+    <row r="37" spans="1:29">
       <c r="A37" s="1">
         <v>46068.54623365741</v>
       </c>
@@ -3044,14 +3620,29 @@
       <c r="U37">
         <v>389.8918133059174</v>
       </c>
-      <c r="V37">
-        <v>0.2570752111838873</v>
-      </c>
-      <c r="W37" t="b">
+      <c r="V37" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="38" spans="1:23">
+      <c r="X37">
+        <v>0.249482358</v>
+      </c>
+      <c r="Y37">
+        <v>0.261320176</v>
+      </c>
+      <c r="Z37">
+        <v>0.3612889167105893</v>
+      </c>
+      <c r="AA37">
+        <v>5.918908999999999</v>
+      </c>
+      <c r="AB37">
+        <v>0.06185349643398184</v>
+      </c>
+      <c r="AC37">
+        <v>24.11617188395628</v>
+      </c>
+    </row>
+    <row r="38" spans="1:29">
       <c r="A38" s="1">
         <v>46068.54634997685</v>
       </c>
@@ -3115,14 +3706,29 @@
       <c r="U38">
         <v>390.1728922122708</v>
       </c>
-      <c r="V38">
-        <v>0.4022888929734793</v>
-      </c>
-      <c r="W38" t="b">
+      <c r="V38" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="39" spans="1:23">
+      <c r="X38">
+        <v>0.249489348</v>
+      </c>
+      <c r="Y38">
+        <v>0.261316994</v>
+      </c>
+      <c r="Z38">
+        <v>0.3612914420778067</v>
+      </c>
+      <c r="AA38">
+        <v>5.913822999999994</v>
+      </c>
+      <c r="AB38">
+        <v>0.06190572320314142</v>
+      </c>
+      <c r="AC38">
+        <v>24.15393506666197</v>
+      </c>
+    </row>
+    <row r="39" spans="1:29">
       <c r="A39" s="1">
         <v>46068.5464662963</v>
       </c>
@@ -3186,14 +3792,29 @@
       <c r="U39">
         <v>390.1059107180673</v>
       </c>
-      <c r="V39">
-        <v>0.1468159698678568</v>
-      </c>
-      <c r="W39" t="b">
+      <c r="V39" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="40" spans="1:23">
+      <c r="X39">
+        <v>0.249485536</v>
+      </c>
+      <c r="Y39">
+        <v>0.261311902</v>
+      </c>
+      <c r="Z39">
+        <v>0.3612851267351936</v>
+      </c>
+      <c r="AA39">
+        <v>5.913183000000004</v>
+      </c>
+      <c r="AB39">
+        <v>0.0619111946165785</v>
+      </c>
+      <c r="AC39">
+        <v>24.15192295954386</v>
+      </c>
+    </row>
+    <row r="40" spans="1:29">
       <c r="A40" s="1">
         <v>46068.54658261574</v>
       </c>
@@ -3257,14 +3878,29 @@
       <c r="U40">
         <v>390.648016757107</v>
       </c>
-      <c r="V40">
-        <v>0.2955528185261374</v>
-      </c>
-      <c r="W40" t="b">
+      <c r="V40" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="41" spans="1:23">
+      <c r="X40">
+        <v>0.249479816</v>
+      </c>
+      <c r="Y40">
+        <v>0.261303626</v>
+      </c>
+      <c r="Z40">
+        <v>0.3612751908893576</v>
+      </c>
+      <c r="AA40">
+        <v>5.911904999999997</v>
+      </c>
+      <c r="AB40">
+        <v>0.0619225704836282</v>
+      </c>
+      <c r="AC40">
+        <v>24.18992935193153</v>
+      </c>
+    </row>
+    <row r="41" spans="1:29">
       <c r="A41" s="1">
         <v>46068.54669893518</v>
       </c>
@@ -3328,14 +3964,29 @@
       <c r="U41">
         <v>391.0422541249104</v>
       </c>
-      <c r="V41">
-        <v>0.4701136449966776</v>
-      </c>
-      <c r="W41" t="b">
+      <c r="V41" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="42" spans="1:23">
+      <c r="X41">
+        <v>0.249497926</v>
+      </c>
+      <c r="Y41">
+        <v>0.261323996</v>
+      </c>
+      <c r="Z41">
+        <v>0.3613024300550849</v>
+      </c>
+      <c r="AA41">
+        <v>5.913034999999994</v>
+      </c>
+      <c r="AB41">
+        <v>0.06191559167194789</v>
+      </c>
+      <c r="AC41">
+        <v>24.21161253287603</v>
+      </c>
+    </row>
+    <row r="42" spans="1:29">
       <c r="A42" s="1">
         <v>46068.54681467592</v>
       </c>
@@ -3399,14 +4050,29 @@
       <c r="U42">
         <v>389.4155799578216</v>
       </c>
-      <c r="V42">
-        <v>0.8485666750740019</v>
-      </c>
-      <c r="W42" t="b">
+      <c r="V42" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="43" spans="1:23">
+      <c r="X42">
+        <v>0.249510636</v>
+      </c>
+      <c r="Y42">
+        <v>0.261330998</v>
+      </c>
+      <c r="Z42">
+        <v>0.3613162714199299</v>
+      </c>
+      <c r="AA42">
+        <v>5.910180999999994</v>
+      </c>
+      <c r="AB42">
+        <v>0.06194702192791736</v>
+      </c>
+      <c r="AC42">
+        <v>24.12313547071983</v>
+      </c>
+    </row>
+    <row r="43" spans="1:29">
       <c r="A43" s="1">
         <v>46068.54693041667</v>
       </c>
@@ -3470,14 +4136,29 @@
       <c r="U43">
         <v>389.9322330886045</v>
       </c>
-      <c r="V43">
-        <v>0.8311784810798165</v>
-      </c>
-      <c r="W43" t="b">
+      <c r="V43" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="44" spans="1:23">
+      <c r="X43">
+        <v>0.249528428</v>
+      </c>
+      <c r="Y43">
+        <v>0.261347548</v>
+      </c>
+      <c r="Z43">
+        <v>0.3613405280698022</v>
+      </c>
+      <c r="AA43">
+        <v>5.909559999999999</v>
+      </c>
+      <c r="AB43">
+        <v>0.06195741276572008</v>
+      </c>
+      <c r="AC43">
+        <v>24.15919231612964</v>
+      </c>
+    </row>
+    <row r="44" spans="1:29">
       <c r="A44" s="1">
         <v>46068.54704615741</v>
       </c>
@@ -3541,14 +4222,29 @@
       <c r="U44">
         <v>389.660505449934</v>
       </c>
-      <c r="V44">
-        <v>0.2584424061724334</v>
-      </c>
-      <c r="W44" t="b">
+      <c r="V44" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="45" spans="1:23">
+      <c r="X44">
+        <v>0.249544632</v>
+      </c>
+      <c r="Y44">
+        <v>0.261354868</v>
+      </c>
+      <c r="Z44">
+        <v>0.3613570123677038</v>
+      </c>
+      <c r="AA44">
+        <v>5.905118000000002</v>
+      </c>
+      <c r="AB44">
+        <v>0.06200556023871864</v>
+      </c>
+      <c r="AC44">
+        <v>24.16111794332544</v>
+      </c>
+    </row>
+    <row r="45" spans="1:29">
       <c r="A45" s="1">
         <v>46068.54716247685</v>
       </c>
@@ -3612,14 +4308,29 @@
       <c r="U45">
         <v>389.8396576869958</v>
       </c>
-      <c r="V45">
-        <v>0.1381434270618137</v>
-      </c>
-      <c r="W45" t="b">
+      <c r="V45" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="46" spans="1:23">
+      <c r="X45">
+        <v>0.249552574</v>
+      </c>
+      <c r="Y45">
+        <v>0.261358688</v>
+      </c>
+      <c r="Z45">
+        <v>0.3613652597900175</v>
+      </c>
+      <c r="AA45">
+        <v>5.903056999999997</v>
+      </c>
+      <c r="AB45">
+        <v>0.06202802481322402</v>
+      </c>
+      <c r="AC45">
+        <v>24.18098396018774</v>
+      </c>
+    </row>
+    <row r="46" spans="1:29">
       <c r="A46" s="1">
         <v>46068.54727821759</v>
       </c>
@@ -3683,14 +4394,29 @@
       <c r="U46">
         <v>387.4775430086098</v>
       </c>
-      <c r="V46">
-        <v>1.315104957669476</v>
-      </c>
-      <c r="W46" t="b">
+      <c r="V46" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="47" spans="1:23">
+      <c r="X46">
+        <v>0.249556704</v>
+      </c>
+      <c r="Y46">
+        <v>0.26135837</v>
+      </c>
+      <c r="Z46">
+        <v>0.3613678819159231</v>
+      </c>
+      <c r="AA46">
+        <v>5.900832999999999</v>
+      </c>
+      <c r="AB46">
+        <v>0.06205123397033528</v>
+      </c>
+      <c r="AC46">
+        <v>24.04345967947789</v>
+      </c>
+    </row>
+    <row r="47" spans="1:29">
       <c r="A47" s="1">
         <v>46068.54739453704</v>
       </c>
@@ -3754,14 +4480,29 @@
       <c r="U47">
         <v>388.0595446166536</v>
       </c>
-      <c r="V47">
-        <v>1.23065796553534</v>
-      </c>
-      <c r="W47" t="b">
+      <c r="V47" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="48" spans="1:23">
+      <c r="X47">
+        <v>0.24956433</v>
+      </c>
+      <c r="Y47">
+        <v>0.261356778</v>
+      </c>
+      <c r="Z47">
+        <v>0.3613719969987854</v>
+      </c>
+      <c r="AA47">
+        <v>5.896224000000004</v>
+      </c>
+      <c r="AB47">
+        <v>0.06209916814082243</v>
+      </c>
+      <c r="AC47">
+        <v>24.09817490980056</v>
+      </c>
+    </row>
+    <row r="48" spans="1:29">
       <c r="A48" s="1">
         <v>46068.54751027778</v>
       </c>
@@ -3825,14 +4566,29 @@
       <c r="U48">
         <v>388.3461517474627</v>
       </c>
-      <c r="V48">
-        <v>0.4425966298270824</v>
-      </c>
-      <c r="W48" t="b">
+      <c r="V48" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="49" spans="1:23">
+      <c r="X48">
+        <v>0.249550668</v>
+      </c>
+      <c r="Y48">
+        <v>0.26136028</v>
+      </c>
+      <c r="Z48">
+        <v>0.3613650949675752</v>
+      </c>
+      <c r="AA48">
+        <v>5.904806000000001</v>
+      </c>
+      <c r="AB48">
+        <v>0.06201010219553484</v>
+      </c>
+      <c r="AC48">
+        <v>24.08138455710285</v>
+      </c>
+    </row>
+    <row r="49" spans="1:29">
       <c r="A49" s="1">
         <v>46068.54762601852</v>
       </c>
@@ -3896,14 +4652,29 @@
       <c r="U49">
         <v>388.4641571816777</v>
       </c>
-      <c r="V49">
-        <v>0.2080786140331646</v>
-      </c>
-      <c r="W49" t="b">
+      <c r="V49" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="50" spans="1:23">
+      <c r="X49">
+        <v>0.249563376</v>
+      </c>
+      <c r="Y49">
+        <v>0.261357734</v>
+      </c>
+      <c r="Z49">
+        <v>0.3613720295791197</v>
+      </c>
+      <c r="AA49">
+        <v>5.897178999999994</v>
+      </c>
+      <c r="AB49">
+        <v>0.0620893779400373</v>
+      </c>
+      <c r="AC49">
+        <v>24.11949787141124</v>
+      </c>
+    </row>
+    <row r="50" spans="1:29">
       <c r="A50" s="1">
         <v>46068.54774175926</v>
       </c>
@@ -3967,14 +4738,29 @@
       <c r="U50">
         <v>388.6302341345984</v>
       </c>
-      <c r="V50">
-        <v>0.1427174594982575</v>
-      </c>
-      <c r="W50" t="b">
+      <c r="V50" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="51" spans="1:23">
+      <c r="X50">
+        <v>0.249559246</v>
+      </c>
+      <c r="Y50">
+        <v>0.2613676</v>
+      </c>
+      <c r="Z50">
+        <v>0.3613763129949839</v>
+      </c>
+      <c r="AA50">
+        <v>5.904176999999997</v>
+      </c>
+      <c r="AB50">
+        <v>0.06201841178536621</v>
+      </c>
+      <c r="AC50">
+        <v>24.10222989280281</v>
+      </c>
+    </row>
+    <row r="51" spans="1:29">
       <c r="A51" s="1">
         <v>46068.5478580787</v>
       </c>
@@ -4038,14 +4824,29 @@
       <c r="U51">
         <v>388.5999941247544</v>
       </c>
-      <c r="V51">
-        <v>0.08845685161759546</v>
-      </c>
-      <c r="W51" t="b">
+      <c r="V51" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="52" spans="1:23">
+      <c r="X51">
+        <v>0.249562742</v>
+      </c>
+      <c r="Y51">
+        <v>0.261368874</v>
+      </c>
+      <c r="Z51">
+        <v>0.3613796486945363</v>
+      </c>
+      <c r="AA51">
+        <v>5.903066000000003</v>
+      </c>
+      <c r="AB51">
+        <v>0.06203033834759721</v>
+      </c>
+      <c r="AC51">
+        <v>24.1049891174328</v>
+      </c>
+    </row>
+    <row r="52" spans="1:29">
       <c r="A52" s="1">
         <v>46068.54797439815</v>
       </c>
@@ -4109,14 +4910,29 @@
       <c r="U52">
         <v>387.8790999170091</v>
       </c>
-      <c r="V52">
-        <v>0.425206916255116</v>
-      </c>
-      <c r="W52" t="b">
+      <c r="V52" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="53" spans="1:23">
+      <c r="X52">
+        <v>0.249563376</v>
+      </c>
+      <c r="Y52">
+        <v>0.261367282</v>
+      </c>
+      <c r="Z52">
+        <v>0.361378935109097</v>
+      </c>
+      <c r="AA52">
+        <v>5.901952999999999</v>
+      </c>
+      <c r="AB52">
+        <v>0.06204161281775047</v>
+      </c>
+      <c r="AC52">
+        <v>24.06464493714863</v>
+      </c>
+    </row>
+    <row r="53" spans="1:29">
       <c r="A53" s="1">
         <v>46068.5480907176</v>
       </c>
@@ -4180,14 +4996,29 @@
       <c r="U53">
         <v>387.5391338553429</v>
       </c>
-      <c r="V53">
-        <v>0.5417086998653732</v>
-      </c>
-      <c r="W53" t="b">
+      <c r="V53" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="54" spans="1:23">
+      <c r="X53">
+        <v>0.249568142</v>
+      </c>
+      <c r="Y53">
+        <v>0.261367918</v>
+      </c>
+      <c r="Z53">
+        <v>0.3613826864433144</v>
+      </c>
+      <c r="AA53">
+        <v>5.899888000000004</v>
+      </c>
+      <c r="AB53">
+        <v>0.06206339126589472</v>
+      </c>
+      <c r="AC53">
+        <v>24.05199289531009</v>
+      </c>
+    </row>
+    <row r="54" spans="1:29">
       <c r="A54" s="1">
         <v>46068.54820645833</v>
       </c>
@@ -4251,14 +5082,29 @@
       <c r="U54">
         <v>387.7868178044623</v>
       </c>
-      <c r="V54">
-        <v>0.175803038478703</v>
-      </c>
-      <c r="W54" t="b">
+      <c r="V54" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="55" spans="1:23">
+      <c r="X54">
+        <v>0.249587524</v>
+      </c>
+      <c r="Y54">
+        <v>0.261369192</v>
+      </c>
+      <c r="Z54">
+        <v>0.3613969931573635</v>
+      </c>
+      <c r="AA54">
+        <v>5.890833999999998</v>
+      </c>
+      <c r="AB54">
+        <v>0.06215870287856419</v>
+      </c>
+      <c r="AC54">
+        <v>24.10432558813148</v>
+      </c>
+    </row>
+    <row r="55" spans="1:29">
       <c r="A55" s="1">
         <v>46068.54832277778</v>
       </c>
@@ -4322,14 +5168,29 @@
       <c r="U55">
         <v>387.339688152334</v>
       </c>
-      <c r="V55">
-        <v>0.223998085151871</v>
-      </c>
-      <c r="W55" t="b">
+      <c r="V55" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="56" spans="1:23">
+      <c r="X55">
+        <v>0.249583712</v>
+      </c>
+      <c r="Y55">
+        <v>0.26136569</v>
+      </c>
+      <c r="Z55">
+        <v>0.3613918278058803</v>
+      </c>
+      <c r="AA55">
+        <v>5.890988999999998</v>
+      </c>
+      <c r="AB55">
+        <v>0.06215624432731556</v>
+      </c>
+      <c r="AC55">
+        <v>24.07558029446269</v>
+      </c>
+    </row>
+    <row r="56" spans="1:29">
       <c r="A56" s="1">
         <v>46068.54843851852</v>
       </c>
@@ -4393,14 +5254,29 @@
       <c r="U56">
         <v>387.87050074084</v>
       </c>
-      <c r="V56">
-        <v>0.2853914749273992</v>
-      </c>
-      <c r="W56" t="b">
+      <c r="V56" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="57" spans="1:23">
+      <c r="X56">
+        <v>0.249577356</v>
+      </c>
+      <c r="Y56">
+        <v>0.26136378</v>
+      </c>
+      <c r="Z56">
+        <v>0.361386056902918</v>
+      </c>
+      <c r="AA56">
+        <v>5.893212000000005</v>
+      </c>
+      <c r="AB56">
+        <v>0.06213243865521084</v>
+      </c>
+      <c r="AC56">
+        <v>24.09934009344615</v>
+      </c>
+    </row>
+    <row r="57" spans="1:29">
       <c r="A57" s="1">
         <v>46068.54855483797</v>
       </c>
@@ -4464,11 +5340,26 @@
       <c r="U57">
         <v>389.0491524251528</v>
       </c>
-      <c r="V57">
-        <v>0.8749523698551902</v>
-      </c>
-      <c r="W57" t="b">
+      <c r="V57" t="b">
         <v>1</v>
+      </c>
+      <c r="X57">
+        <v>0.24957418</v>
+      </c>
+      <c r="Y57">
+        <v>0.261368236</v>
+      </c>
+      <c r="Z57">
+        <v>0.3613870862557544</v>
+      </c>
+      <c r="AA57">
+        <v>5.897027999999999</v>
+      </c>
+      <c r="AB57">
+        <v>0.06209344650300019</v>
+      </c>
+      <c r="AC57">
+        <v>24.15740273314879</v>
       </c>
     </row>
   </sheetData>
